--- a/test/test.xlsx
+++ b/test/test.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\r\node-server-office-js\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jowandy\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841DAA35-7C20-4CF4-BF82-0BCEE32606D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B6957AA-37D2-4B65-9309-C0F15D27E260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="-18120" windowWidth="29040" windowHeight="18240" xr2:uid="{19DECAA8-986A-4E62-B582-B19C412155BD}"/>
+    <workbookView xWindow="4785" yWindow="-18120" windowWidth="29040" windowHeight="18240" xr2:uid="{8157A30B-6986-4DDA-8513-673A09E38441}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,16 +31,11 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Hello World</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -49,7 +44,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -94,9 +89,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -104,39 +99,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -188,7 +183,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -240,7 +235,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -299,13 +294,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -314,6 +302,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -378,91 +373,47 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="1144" row="2">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{79A9AE60-8152-492D-AA2F-FBA3A496E2EB}">
-  <we:reference id="wa200006798" version="1.0.0.0" store="en-US" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200006798" version="1.0.0.0" store="wa200006798" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E0B56E-C4AF-4A32-841A-A68BD4448292}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7A3723-9643-4CEF-9108-8761DB824EA5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<Embed xmlns="TEST">0-1720561079661 New 0</Embed>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<Embed xmlns="http://wandyezj.github.io/schemas/Multiple">0-1720561005817 TEST</Embed>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01LAV6DNT64C27T2W4RVD2EDCSOB2QGNDJ:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9taWNyb3NvZnQtbXkuc2hhcmVwb2ludC1kZi5jb20vOnU6L3Avam93YW5keS9FWDdndGZucTNJMUhvZ3hTY0hVRE5Ha0JLeWxITjZCYVdkQWFrMHc2QWVmWGxR"/>
-</scriptIds>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB30EB7D-08D1-480A-BBE9-81ED254DA17F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="TEST"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C3D2CC8-3236-41FA-9EA2-2493377539F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://wandyezj.github.io/schemas/Multiple"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BFB849C-3DE1-418E-9373-9E21DFC4D5DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/extensibility/maker/v1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{f42aa342-8706-4288-bd11-ebb85995028c}" enabled="1" method="Standard" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
+  <clbl:label id="{87ba5c36-b7cf-4793-bbc2-bd5b3a9f95ca}" enabled="1" method="Privileged" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>